--- a/src/test/resources/configurevenu.xlsx
+++ b/src/test/resources/configurevenu.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="38">
   <si>
     <t>Availability</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>25/12/259, Postal Colony, Vedayapalem, Nellore, Andhra Pradesh 524004, India</t>
+  </si>
+  <si>
+    <t>8555900777</t>
+  </si>
+  <si>
+    <t>C9XR+982, Mega Hills, Madhapur, Hyderabad, Telangana 500081, India</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="25.28515625"/>
@@ -615,52 +621,103 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B7" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C7" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D7" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="E7" t="s" s="0">
         <v>7</v>
       </c>
     </row>
